--- a/src/attributions/attributions_ig_traj_114.xlsx
+++ b/src/attributions/attributions_ig_traj_114.xlsx
@@ -2137,10 +2137,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01739850552444757</v>
+        <v>0.01215806389254927</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2149,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.005742339325050138</v>
+        <v>0.002238927650594487</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.002873034930628433</v>
+        <v>-0.004456225747804633</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -2164,37 +2164,37 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002641372930376825</v>
+        <v>0.0294589524526915</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.01497138712529073</v>
+        <v>0.006696207978047444</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.01378724476227392</v>
+        <v>-0.01465403645998687</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.002137656601023212</v>
+        <v>0.01271399663334733</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2203,10 +2203,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.006981212855439578</v>
+        <v>0.03118578039756497</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.01521607397313131</v>
+        <v>0.01067701723060812</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
@@ -2215,40 +2215,40 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.02192900900209038</v>
+        <v>-0.02824909750628109</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.02555396019091213</v>
+        <v>-0.01551016587287565</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.007598771864582156</v>
+        <v>-0.01843635721179339</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
         <v>-0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.006921543295291488</v>
+        <v>0.003095849665953246</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,13 +2257,13 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01418139489130135</v>
+        <v>-0.02244573507901149</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.002710330579712615</v>
+        <v>-0.006347422820284856</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2275,19 +2275,19 @@
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.05960070425551829</v>
+        <v>0.1075386579909015</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.03301283553006293</v>
+        <v>-0.00310094624918478</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.008320540392149845</v>
+        <v>0.006207473785787527</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2296,28 +2296,28 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.008635538320606652</v>
+        <v>-0.01760950612570002</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.02442935907046026</v>
+        <v>-0.01543022391038045</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.008869074972720948</v>
+        <v>-0.02308473281882403</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
         <v>0</v>
@@ -2329,34 +2329,34 @@
         <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.01914346145913491</v>
+        <v>0.02148914150570869</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.009105909595465252</v>
+        <v>0.04293433119214839</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01460141171641152</v>
+        <v>0.03770438051298652</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU4" t="n">
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>-0.006437270445469941</v>
+        <v>-0.005912580117821944</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,13 +2365,13 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.002372147887940273</v>
+        <v>0.006707498237347042</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.003991101810406048</v>
+        <v>0.005879609483754813</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>0</v>
@@ -2380,49 +2380,49 @@
         <v>-0</v>
       </c>
       <c r="CD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-2.015610064424472e-05</v>
+        <v>-0.008101468355325062</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
         <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001151817854737306</v>
+        <v>-0.005538083154394687</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.01879657934058057</v>
+        <v>0.02202272469417644</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>-0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.01092361311107419</v>
+        <v>-0.01759475307202316</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.01300897547401754</v>
+        <v>0.01948899894055327</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.00750857768303027</v>
+        <v>0.0007504299565544374</v>
       </c>
       <c r="CS4" t="n">
         <v>0</v>
@@ -2431,52 +2431,52 @@
         <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.001300875613105316</v>
+        <v>-0.01060815570881559</v>
       </c>
       <c r="CX4" t="n">
         <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0002453227877442921</v>
+        <v>-0.007600727900872917</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.01853158068859971</v>
+        <v>0.01905823976063582</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.006336494252685357</v>
+        <v>-0.01009787467373154</v>
       </c>
       <c r="DG4" t="n">
         <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.008996302803678032</v>
+        <v>-0.01709406662883393</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.02123245087062119</v>
+        <v>-0.0006812067637406998</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
@@ -2485,67 +2485,67 @@
         <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.008903917328329816</v>
+        <v>-0.003254787106513894</v>
       </c>
       <c r="DP4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0003160984357594222</v>
+        <v>0.01464925975095016</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.007002971127707047</v>
+        <v>0.04669127931707569</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.002798529774703979</v>
+        <v>0.001169486549615281</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.02959668398390957</v>
+        <v>0.01040987882973049</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.005337932667184205</v>
+        <v>-0.02084734234570141</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.0003127639305509337</v>
+        <v>-0.02368404995586836</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
@@ -2554,37 +2554,37 @@
         <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.002596429876014659</v>
+        <v>-0.02090199961842448</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.003262844418450365</v>
+        <v>0.006527660437904499</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN4" t="n">
         <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.004869156295240714</v>
+        <v>0.01264616318841866</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.001381945257301866</v>
+        <v>0.003398922517222558</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.02967482391157765</v>
+        <v>0.01688405819966956</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
@@ -2593,13 +2593,13 @@
         <v>0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.0006967013835980551</v>
+        <v>-0.01238158426587643</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,25 +2608,25 @@
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.0005897138296276736</v>
+        <v>-0.01447602450834842</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.01560091811697879</v>
+        <v>0.01693675862958416</v>
       </c>
       <c r="FD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE4" t="n">
         <v>-0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.02620797728739058</v>
+        <v>-0.02237374268773093</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
@@ -2635,10 +2635,10 @@
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.03619866867127072</v>
+        <v>-0.001692176195926731</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.007132599705005279</v>
+        <v>-0.0194474763597224</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,25 +2647,25 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.0003350869764636546</v>
+        <v>0.0001020197076099431</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.005179798462387117</v>
+        <v>3.621934213460897e-05</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.03356767539091636</v>
+        <v>0.009561702154147388</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2674,25 +2674,25 @@
         <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.01833923974834067</v>
+        <v>0.003761716829047346</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.007042560246551811</v>
+        <v>0.02273671813685144</v>
       </c>
       <c r="GE4" t="n">
         <v>0</v>
@@ -2701,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,22 +2709,22 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1409044453303748</v>
+        <v>0.04023551600346872</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.09159443413022268</v>
+        <v>-0.05121769189733775</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01235022612595298</v>
+        <v>-0.006425643207882196</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2736,22 +2736,22 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1204942024403402</v>
+        <v>0.04917488399764731</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.07842708799723951</v>
+        <v>-0.0560657563049413</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0283735682603045</v>
+        <v>-0.001707981051725749</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2760,22 +2760,22 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0153150678567363</v>
+        <v>0.004755119160905698</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0008350640438035573</v>
+        <v>0.01311802611146711</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01993123572996437</v>
+        <v>0.02483777446465563</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
@@ -2787,19 +2787,19 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.08584742144592239</v>
+        <v>0.001124642175344211</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.05680024210239169</v>
+        <v>-0.00454423386047891</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.08644658795154131</v>
+        <v>-0.01530571970183523</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -2817,16 +2817,16 @@
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01394410691895959</v>
+        <v>0.01760561964375237</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.04192181007344316</v>
+        <v>-0.0441472552606787</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.03248210643864978</v>
+        <v>0.004203450154708076</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -2841,22 +2841,22 @@
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3694732690704549</v>
+        <v>0.1265328188645299</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.03155941004416073</v>
+        <v>-0.09155988412249931</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1540182278081973</v>
+        <v>-0.01590552907411613</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2865,28 +2865,28 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.007663915078643851</v>
+        <v>0.0009926192525851318</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.06949816666800089</v>
+        <v>-0.01449158992169515</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.06632791682304905</v>
+        <v>-0.005502978680917397</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
         <v>0</v>
@@ -2895,25 +2895,25 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.01699724384174043</v>
+        <v>-0.0007761889232760646</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.07279433158847777</v>
+        <v>-0.0006517043706019293</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.08377065136192065</v>
+        <v>0.07019558583303084</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2922,25 +2922,25 @@
         <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.04779072600507383</v>
+        <v>-0.01081284886859297</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.05739533664533413</v>
+        <v>0.05685005625048371</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.005496730125182404</v>
+        <v>0.007447006070558724</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
         <v>0</v>
@@ -2949,82 +2949,82 @@
         <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.08773802312167021</v>
+        <v>-0.04248120805294379</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.01872388778155186</v>
+        <v>0.02947454693475789</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.02774263379435012</v>
+        <v>0.01930129682403693</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0318789598762315</v>
+        <v>-0.03838050501223015</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.06171534558160793</v>
+        <v>0.03864637947979</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1156444770586196</v>
+        <v>0.01897125164190816</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT5" t="n">
         <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.09172941320296943</v>
+        <v>-0.04793367542380973</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.035842666727775</v>
+        <v>0.03502162759335523</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0126453666736176</v>
+        <v>0.01310394717830126</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD5" t="n">
         <v>0</v>
@@ -3033,79 +3033,79 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.004512406944717457</v>
+        <v>-0.001238039167176205</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.03688527384479826</v>
+        <v>0.004966881315788265</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.03284314482253818</v>
+        <v>-0.006169821357441162</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.1377785297253387</v>
+        <v>-0.01428258315701608</v>
       </c>
       <c r="DP5" t="n">
         <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.01197806184298013</v>
+        <v>0.001635026317614438</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.02450218086683585</v>
+        <v>-0.02459085767164659</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU5" t="n">
         <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW5" t="n">
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.006438885416509966</v>
+        <v>0.0237976114121774</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.02587050601633179</v>
+        <v>0.0572536887445694</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0814917448638852</v>
+        <v>-0.003997068738894098</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
@@ -3114,25 +3114,25 @@
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.03130016769014329</v>
+        <v>-0.03549470151464328</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.00263958476147946</v>
+        <v>0.008763273177168501</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.05133306121377285</v>
+        <v>0.008935171721271081</v>
       </c>
       <c r="EK5" t="n">
         <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
@@ -3141,22 +3141,22 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.09281009045915591</v>
+        <v>-0.01098643308433067</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.05704282489107986</v>
+        <v>0.03252052560386038</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.02559175079340365</v>
+        <v>0.01757485735542197</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3165,49 +3165,49 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.09484193985256166</v>
+        <v>-0.05360264715134427</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.0456294111240801</v>
+        <v>0.03195414869119987</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.01776612505630383</v>
+        <v>0.01011003496720224</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.01523409050219039</v>
+        <v>-0.03865697378773981</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.0603214205834819</v>
+        <v>0.02466310432803438</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0492342495665702</v>
+        <v>0.03211403217744991</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
@@ -3219,19 +3219,19 @@
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.002724442131398432</v>
+        <v>0.03081352750813652</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.1049130900066486</v>
+        <v>0.1227213140887902</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.1466005001463694</v>
+        <v>-0.01737166265655049</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
@@ -3249,13 +3249,13 @@
         <v>-0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.02484350941877112</v>
+        <v>-0.03740905924497227</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.01207469195550987</v>
+        <v>-0.005737978791750822</v>
       </c>
       <c r="GC5" t="n">
         <v>0</v>
@@ -3267,10 +3267,10 @@
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01904904689436749</v>
+        <v>0.01912257575363844</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,13 +3287,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0007586192052064278</v>
+        <v>0.006620938750280419</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004269821543246322</v>
+        <v>0.006793281861445677</v>
       </c>
       <c r="G6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -3305,7 +3305,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008879286292526285</v>
+        <v>0.03937687790313287</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,16 +3314,16 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.005923020902331678</v>
+        <v>0.002920509989835877</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.004660932127397947</v>
+        <v>-0.00500407119912304</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0005260718908250357</v>
+        <v>0.002572311161466207</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,52 +3341,52 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.004563043255058226</v>
+        <v>0.008136915787453245</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.008605527385469474</v>
+        <v>-0.001877399191496726</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.02328167373965352</v>
+        <v>-0.03145683804155353</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0146253218392908</v>
+        <v>-0.02859799633124886</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.001791387417008212</v>
+        <v>-0.01128881513018388</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.004938990786855365</v>
+        <v>0.004342215357453055</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -3395,13 +3395,13 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.007964785022715052</v>
+        <v>-0.005580597414263086</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.004118808934580444</v>
+        <v>-0.01035072478932999</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -3410,10 +3410,10 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.05433279448624147</v>
+        <v>0.08470958210440603</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3422,10 +3422,10 @@
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.001529349276824727</v>
+        <v>-0.01242866980508773</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.01137490774360372</v>
+        <v>0.002677666841005565</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3434,28 +3434,28 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.002235038332464088</v>
+        <v>-0.01031388584008723</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF6" t="n">
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.02216431864687115</v>
+        <v>-0.01006985445321527</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.002415429280862369</v>
+        <v>-0.01224009578049138</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
         <v>0</v>
@@ -3464,37 +3464,37 @@
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.008233161443335718</v>
+        <v>0.01978139704685087</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.006370045996792021</v>
+        <v>0.04177217271564029</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.008013766426333767</v>
+        <v>0.02741255389358337</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.004795332767695523</v>
+        <v>-0.008481682903494266</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0007096285440589249</v>
+        <v>0.001671893959836711</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.001725452357147309</v>
+        <v>0.004318768059295128</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,22 +3521,22 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.002103875267177468</v>
+        <v>-0.008459418760110637</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
         <v>0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.004540114263366529</v>
+        <v>-0.006353374644135129</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.009127082346019673</v>
+        <v>0.01822308624794026</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3545,52 +3545,52 @@
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.006892867125634539</v>
+        <v>-0.01609140339662743</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
         <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.0004924948927284749</v>
+        <v>0.01738241679335358</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.01259362693183778</v>
+        <v>0.00649907546557507</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
         <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.0005968914496668703</v>
+        <v>-0.01020083938148487</v>
       </c>
       <c r="CX6" t="n">
         <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.00695007752276067</v>
+        <v>-0.005187529098507926</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.01115245119350684</v>
+        <v>0.01472096983090587</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
         <v>0</v>
@@ -3599,22 +3599,22 @@
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.01050559834760885</v>
+        <v>-0.01162183326815388</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>7.732319973330312e-05</v>
+        <v>-0.001235120153578878</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.03485440364439656</v>
+        <v>0.007792522153718303</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,31 +3623,31 @@
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.01023139315337122</v>
+        <v>-0.006997017979391114</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.002928408402360509</v>
+        <v>0.004664785040323925</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.003646566908747039</v>
+        <v>0.03519427332082769</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV6" t="n">
         <v>-0</v>
@@ -3656,61 +3656,61 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.01435306296823524</v>
+        <v>-0.00763650687936261</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.01126672740608696</v>
+        <v>0.01020359503309745</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.008980188302475782</v>
+        <v>0.0133526546311653</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.0005765092005802435</v>
+        <v>-0.01598784411630681</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.002745595360562966</v>
+        <v>-0.01164790627239241</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.0008820768848152225</v>
+        <v>0.004531492347828082</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.01000612404023353</v>
+        <v>0.004851940999676645</v>
       </c>
       <c r="EQ6" t="n">
         <v>-0</v>
@@ -3719,25 +3719,25 @@
         <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.01402906001765609</v>
+        <v>-0.00908403635012142</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.03351666059857906</v>
+        <v>0.01417027367274854</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.002604564902636275</v>
+        <v>-0.0133351419702445</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
@@ -3746,37 +3746,37 @@
         <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.007397723557009846</v>
+        <v>-0.01323887640498987</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.008844728530256663</v>
+        <v>0.01290545580901309</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
         <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.02036503234960488</v>
+        <v>-0.02148468540476401</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.01769008399657494</v>
+        <v>0.01286516230870846</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.02009829347894437</v>
+        <v>0.009741581900015979</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
@@ -3785,25 +3785,25 @@
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.001554424516638812</v>
+        <v>0.003136209828215079</v>
       </c>
       <c r="FR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS6" t="n">
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.01212815937724983</v>
+        <v>0.005779494997890882</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.01170906163065928</v>
+        <v>-0.01128745349275705</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3812,42 +3812,42 @@
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.01637242442215818</v>
+        <v>0.002070130206844272</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.005412338783210733</v>
+        <v>0.01735823042228819</v>
       </c>
       <c r="GE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF6" t="n">
         <v>0</v>
       </c>
       <c r="GG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.08514066380563266</v>
+        <v>0.02266634097586993</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,25 +3856,25 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.006504502584473776</v>
+        <v>-0.004191567369535462</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02987236098694643</v>
+        <v>0.003775786515632826</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0450960194749587</v>
+        <v>0.04128278502994599</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.06299203260168069</v>
+        <v>-0.008836991847998781</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3892,16 +3892,16 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.01230716161193877</v>
+        <v>-0.0002804155743392259</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.003948937940933446</v>
+        <v>0.0003836899082401698</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
@@ -3910,34 +3910,34 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01303672419227266</v>
+        <v>0.00727568497247641</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.006494583501457419</v>
+        <v>0.0006916533481508191</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.07095150743648922</v>
+        <v>-0.01777191927100903</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02851849278576666</v>
+        <v>-0.009194408548242303</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -3946,16 +3946,16 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.02294168317366611</v>
+        <v>0.0008085026250401338</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.03977983198782763</v>
+        <v>0.01608626117581832</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,37 +3964,37 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.0290732683045924</v>
+        <v>-0.002971770095208235</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.0182441094296223</v>
+        <v>-0.00741907940665442</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.2410543406198931</v>
+        <v>0.09235130351430113</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1207228411724405</v>
+        <v>-0.008363235698910395</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,67 +4003,67 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.00604645310268722</v>
+        <v>0.004192489393486078</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.04429596569276322</v>
+        <v>-0.01609416026041282</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.09532769357686441</v>
+        <v>-0.009857622650990435</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
         <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.02972520037016202</v>
+        <v>-0.007319379020884512</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.03270516376531708</v>
+        <v>0.005580180043564202</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1093826317437907</v>
+        <v>0.02572915212991377</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.01817107437092769</v>
+        <v>0.008036488687694528</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.02601289155964639</v>
+        <v>-0.009376946092577353</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
@@ -4072,25 +4072,25 @@
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.001192303994262786</v>
+        <v>0.004225105883908096</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0.005501877591478925</v>
+        <v>0.002337858579075188</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.03331674879899296</v>
+        <v>-0.01562965286347398</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
@@ -4099,10 +4099,10 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.005122385098894132</v>
+        <v>0.002006700152116804</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
@@ -4111,49 +4111,49 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.04487532099585066</v>
+        <v>0.01037462179046397</v>
       </c>
       <c r="CM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.008403490821796724</v>
+        <v>-0.02418341507748643</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.01981380439422476</v>
+        <v>0.003932313580472395</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT7" t="n">
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.009086629140398339</v>
+        <v>0.02375329629529302</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.04084965873120205</v>
+        <v>-0.01581563697001144</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.007982490482278878</v>
+        <v>0.00208890117311195</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
@@ -4165,148 +4165,148 @@
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0354717157047994</v>
+        <v>0.008714185941746206</v>
       </c>
       <c r="DE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.05967765031743179</v>
+        <v>-0.01208504577855415</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.05098776593641139</v>
+        <v>0.0008000177693699345</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.01648530782068989</v>
+        <v>-0.01404941884533872</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.02507535565767952</v>
+        <v>-0.00587815799642235</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.02410008480086345</v>
+        <v>0.006504707607360778</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0.03160470545230103</v>
+        <v>-0.01242301288315955</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.02492855915402125</v>
+        <v>-0.001865013476885702</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
         <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.02302656524779656</v>
+        <v>0.003438343589681624</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.01216883376053566</v>
+        <v>0.00682755300321726</v>
       </c>
       <c r="EF7" t="n">
         <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.02043752852711681</v>
+        <v>-0.02100867127398863</v>
       </c>
       <c r="EH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.03040781621295028</v>
+        <v>-0.00396828963670707</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.04627476573106086</v>
+        <v>0.009403655633834896</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.07081247848223471</v>
+        <v>-0.004301369007596035</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.009247352182649615</v>
+        <v>0.01030589552995605</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.05103334439994429</v>
+        <v>0.004044316362015723</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.05253228089023151</v>
+        <v>-0.01954430875420683</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,34 +4315,34 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.005228010507863306</v>
+        <v>-0.002663877567425017</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.02248690864656036</v>
+        <v>0.00926474827946651</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.07491157824680332</v>
+        <v>-0.01726426906022709</v>
       </c>
       <c r="FI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.007264804774371004</v>
+        <v>-0.001347631241224963</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
@@ -4351,25 +4351,25 @@
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.04478282437946282</v>
+        <v>0.03320156026558923</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.06540306828357749</v>
+        <v>0.01189896896347097</v>
       </c>
       <c r="FR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS7" t="n">
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.07755682145994583</v>
+        <v>-0.003707755668744147</v>
       </c>
       <c r="FU7" t="n">
         <v>-0</v>
@@ -4381,16 +4381,16 @@
         <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.004190790431210084</v>
+        <v>0.0005001871876079453</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.06165555661527833</v>
+        <v>-0.0004921622136971766</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.03879564429339376</v>
+        <v>-0.001810982743776762</v>
       </c>
     </row>
     <row r="8">
@@ -4985,16 +4985,16 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2785117865523513</v>
+        <v>0.07484868666562229</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1432577114387407</v>
+        <v>-0.07138611784086184</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.05494103971449385</v>
+        <v>0.002943597687872126</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -5003,7 +5003,7 @@
         <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -5012,19 +5012,19 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2271498121730594</v>
+        <v>0.09009891180743872</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1692641082272083</v>
+        <v>-0.1017911686520526</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.08867930885519551</v>
+        <v>0.002865549511512548</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P9" t="n">
         <v>-0</v>
@@ -5036,25 +5036,25 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.006901640901540006</v>
+        <v>0.0005322950530884862</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002865187419728073</v>
+        <v>0.005243440326508727</v>
       </c>
       <c r="W9" t="n">
-        <v>-5.195247140712843e-11</v>
+        <v>-4.07848799230046e-11</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -5066,43 +5066,43 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1403311569291864</v>
+        <v>0.007043492345193928</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0529030200876849</v>
+        <v>-0.01188067913389455</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.02357427540096167</v>
+        <v>-0.01367613653929769</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.03544009836987062</v>
+        <v>0.03806902648307395</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.03549781832549769</v>
+        <v>-0.05632088313883323</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.07073920452920754</v>
+        <v>0.006842547768114268</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5117,22 +5117,22 @@
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.4987015971079656</v>
+        <v>0.1246146657928708</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.007064639793640371</v>
+        <v>-0.06807183994852531</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1331394259571219</v>
+        <v>-0.05503346101187083</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -5141,22 +5141,22 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.006939878045736839</v>
+        <v>0.00747506138725461</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.09386589299441743</v>
+        <v>-0.002423933178329152</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1859840940023128</v>
+        <v>0.005554633313503871</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.06455133797851413</v>
+        <v>0.01032457849778092</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.06279404938572214</v>
+        <v>0.003266133532536083</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.08714237839627059</v>
+        <v>0.05174372362506721</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,22 +5201,22 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>-0.05347687963596548</v>
+        <v>-0.02018421343853769</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.06586065111483112</v>
+        <v>0.09625399774911825</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.01126749968165838</v>
+        <v>0.009158485622150502</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
@@ -5228,46 +5228,46 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.1090345126166126</v>
+        <v>-0.0513719686180918</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.01470363077633756</v>
+        <v>0.06440819401632246</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.008703644099524739</v>
+        <v>0.005405238971227431</v>
       </c>
       <c r="CI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.03069818938430116</v>
+        <v>-0.06309531381401738</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.1605585063691602</v>
+        <v>0.1148380996450476</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.1144066924424921</v>
+        <v>0.0240879521198779</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
@@ -5276,55 +5276,55 @@
         <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.09492637125717281</v>
+        <v>-0.04643812847050958</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0370723311699576</v>
+        <v>0.06487728305903956</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.00892548159175648</v>
+        <v>0.005863240462149203</v>
       </c>
       <c r="DA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.008339816040856367</v>
+        <v>-0.001292806169901413</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.0933157780835456</v>
+        <v>0.01066952315554717</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.02204069653503572</v>
+        <v>-0.03735932597050307</v>
       </c>
       <c r="DJ9" t="n">
         <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
@@ -5336,16 +5336,16 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.1044418239251887</v>
+        <v>-0.05076034784324018</v>
       </c>
       <c r="DP9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.01340417576505098</v>
+        <v>0.04588851674333751</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.01669833259571806</v>
+        <v>0.0003119506725958578</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -5360,79 +5360,79 @@
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.04370286898197853</v>
+        <v>-0.009707343914413902</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.01218519731781227</v>
+        <v>0.04496292734893052</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.1103628271689794</v>
+        <v>0.001112901759303755</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.04537489249841273</v>
+        <v>-0.01888624464314152</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.009314443078928506</v>
+        <v>0.03851267828304722</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.02980757006620184</v>
+        <v>0.01676701760031053</v>
       </c>
       <c r="EK9" t="n">
         <v>-0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>-0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO9" t="n">
         <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.07698505852704557</v>
+        <v>-0.04089791847892638</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.0453478796940911</v>
+        <v>-0.04175365522279105</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.03174507369533967</v>
+        <v>0.03504447359651033</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,70 +5444,70 @@
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.09469292448661615</v>
+        <v>-0.05576260742842395</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.02597374077392445</v>
+        <v>0.07626479348654004</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.002559192218680078</v>
+        <v>0.002359493196560552</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.05427355580368762</v>
+        <v>-0.02996136393890192</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.03968464771876511</v>
+        <v>0.002403464351017391</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.1471711600862315</v>
+        <v>-0.02353666190782347</v>
       </c>
       <c r="FL9" t="n">
         <v>0</v>
       </c>
       <c r="FM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN9" t="n">
         <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
         <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.05635314101895284</v>
+        <v>0.0274547386959142</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.06865864645205759</v>
+        <v>0.09820186720737362</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.2362630241581652</v>
+        <v>-0.0322912930489202</v>
       </c>
       <c r="FU9" t="n">
         <v>-0</v>
@@ -5522,16 +5522,16 @@
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.001425183784971725</v>
+        <v>-0.02713196811770968</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.01962287544667134</v>
+        <v>0.007009818075059453</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
@@ -5543,10 +5543,10 @@
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,79 +5554,79 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2745253914044014</v>
+        <v>0.06933546715055539</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1449605846994911</v>
+        <v>-0.03202321447854998</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1224351501019365</v>
+        <v>-0.007814925898566524</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01847815555385294</v>
+        <v>0.00988706451863159</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1797731358886533</v>
+        <v>0.07703384147228907</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1363022724538857</v>
+        <v>-0.07160723838862822</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1492260053023874</v>
+        <v>-0.004579127928984276</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.00465871508841684</v>
+        <v>0.003828382911335698</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01523961045896981</v>
+        <v>0.002542286953358325</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.007826391182294208</v>
+        <v>-0.008387726687940397</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.01496902919642264</v>
+        <v>-0.013082153123472</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0440058512652355</v>
+        <v>0.04855927479581765</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -5635,52 +5635,52 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.04094549484929661</v>
+        <v>-0.008286428152987496</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0556559707213999</v>
+        <v>0.0006407790401960086</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.007905508479260743</v>
+        <v>-0.1059855545932963</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.02675425200446559</v>
+        <v>0.003038978687210501</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.001702180926879293</v>
+        <v>0.03640540458424619</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.04426783777773425</v>
+        <v>-0.02237373793013208</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.08117777466235107</v>
+        <v>0.004871940434167629</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.02615862935596336</v>
+        <v>-0.01622830857672104</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,433 +5689,433 @@
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.2496530827979242</v>
+        <v>0.09576468740317526</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.02434894070762251</v>
+        <v>-0.009649785860030909</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.03189908640615327</v>
+        <v>-0.0538918262461694</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0.1061167037674458</v>
+        <v>-0.05743847003898492</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.02607377524774786</v>
+        <v>-0.0151081050030655</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.1032070929955103</v>
+        <v>-0.008165694690359325</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.2273554842775277</v>
+        <v>-0.04804298753197244</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.002561009173256118</v>
+        <v>-0.006447690324956314</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.1317056847353663</v>
+        <v>0.03333080682288839</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.1329982972479603</v>
+        <v>0.001284382065736406</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.03253170062200614</v>
+        <v>0.03012411630233636</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.03032139262694911</v>
+        <v>0.02841525167107237</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.07587110340410218</v>
+        <v>0.03250900932206217</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.01500711288948846</v>
+        <v>0.01508415171231564</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.03194098070229598</v>
+        <v>0.01891698458110074</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.01641544521761219</v>
+        <v>0.01530560174481621</v>
       </c>
       <c r="CC10" t="n">
         <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.08451711929851143</v>
+        <v>-0.02962982046951156</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.02733597780248888</v>
+        <v>0.01738418063393486</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.003635503615845289</v>
+        <v>0.006360291068842787</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.02065220098070933</v>
+        <v>0.008119014161556864</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.09775504703166843</v>
+        <v>-0.04869741155899067</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.03580565328622332</v>
+        <v>0.02633422348182899</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.0385509329121776</v>
+        <v>0.09177605989964938</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.03535243228993902</v>
+        <v>0.05555583380122395</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.06954687948307403</v>
+        <v>-0.03031090003636066</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.05458244577706018</v>
+        <v>0.02092136833630611</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.001091956466000038</v>
+        <v>0.008402834217657314</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.02104462064016124</v>
+        <v>0.001101927302659186</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.09675253162293691</v>
+        <v>-0.01270438955712783</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.06552879219270215</v>
+        <v>0.005868995398865665</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.01577391593934169</v>
+        <v>-0.006917557340003019</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0.001850629672211744</v>
+        <v>-0.005506897795946934</v>
       </c>
       <c r="DM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.07486613394640501</v>
+        <v>-0.01718056416389546</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.02209664057765293</v>
+        <v>0.006162065829889246</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.05552652152020453</v>
+        <v>-0.04421858676682489</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
       </c>
       <c r="DT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.02362958519955357</v>
+        <v>0.06281466120704685</v>
       </c>
       <c r="DV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.05271917626728646</v>
+        <v>0.02062762849316072</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.06861089512605004</v>
+        <v>0.03604833349534336</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.1051861376816593</v>
+        <v>-0.02627990565479777</v>
       </c>
       <c r="EB10" t="n">
         <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.03293490282061057</v>
+        <v>0.07259753496334165</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.02498733826670445</v>
+        <v>-0.004112787524519894</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0.00477319077336208</v>
+        <v>0.003183387747545395</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.02716074550046153</v>
+        <v>-0.02965556250944343</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.06561278366840263</v>
+        <v>0.01000603910668414</v>
       </c>
       <c r="EN10" t="n">
         <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.111357159385348</v>
+        <v>-0.001203926262530877</v>
       </c>
       <c r="EQ10" t="n">
         <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.052937600675882</v>
+        <v>0.01502650776746551</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.02151764540172563</v>
+        <v>0.01224848253825553</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0.008792222223021598</v>
+        <v>0.01723085788556988</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.07541156500817491</v>
+        <v>-0.03873653962162123</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.06137415558777666</v>
+        <v>0.02257978329058696</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.01944123988631179</v>
+        <v>0.006567267905482568</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.01471003988619573</v>
+        <v>0.005116584757240866</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.05664064162543751</v>
+        <v>-0.02375170029463401</v>
       </c>
       <c r="FI10" t="n">
         <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.05070934129762763</v>
+        <v>0.008011515373934132</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.09478704247136337</v>
+        <v>0.04988625631830564</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.02464140904851663</v>
+        <v>-0.004254469850731016</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.05969897940765066</v>
+        <v>0.01756330828217392</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.001791293593768653</v>
+        <v>0.09444249458053398</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.04536098641690913</v>
+        <v>-0.07367475428776758</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.1262741690430763</v>
+        <v>0.0235671302921658</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.02221495370885925</v>
+        <v>-0.0135571901949556</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.005412081458538316</v>
+        <v>-0.02953721861222602</v>
       </c>
       <c r="GC10" t="n">
         <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.111319346209194</v>
+        <v>-0.00688873432314361</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02540000141573279</v>
+        <v>0.2604903391261886</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -6132,16 +6132,16 @@
         <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.07499936073843123</v>
+        <v>0.06430612079757038</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.05870595944715889</v>
+        <v>-0.2340080780889728</v>
       </c>
       <c r="G11" t="n">
         <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0374443159699336</v>
+        <v>0.2752632182399198</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,13 +6159,13 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.08855585402626022</v>
+        <v>0.02492509532952704</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.05372925941006011</v>
+        <v>-0.1929239853739146</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>-0</v>
@@ -6174,10 +6174,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.002127093029519373</v>
+        <v>0.01172454316159</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -6186,52 +6186,52 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.003927999781010699</v>
+        <v>-0.03308161913510829</v>
       </c>
       <c r="X11" t="n">
-        <v>0.003233983465786348</v>
+        <v>-0.006597886571864262</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.05449645777213624</v>
+        <v>-0.02270403321520806</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.05196605564680572</v>
+        <v>-0.1627501337288159</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.02569733197834966</v>
+        <v>0.05445073288114072</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.01633082850504183</v>
+        <v>0.05564210295969251</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,25 +6240,25 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.05145438852679684</v>
+        <v>-0.03742490028647857</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.01151497426360289</v>
+        <v>-0.02643040524824328</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.06312401734160317</v>
+        <v>0.2528607203860582</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -6267,43 +6267,43 @@
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.07046970651706097</v>
+        <v>-0.0506039665590292</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.003258460864160961</v>
+        <v>-0.04739135935424602</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.005649737267705692</v>
+        <v>0.06721418118549596</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.05837337683290886</v>
+        <v>-0.03771084028453935</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.08285126565418419</v>
+        <v>-0.1671253218252276</v>
       </c>
       <c r="BI11" t="n">
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
@@ -6312,34 +6312,34 @@
         <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.08997317702874659</v>
+        <v>0.05250215928603871</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.046952661706695</v>
+        <v>0.1319666369992952</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.04194148483330557</v>
+        <v>0.08591118716768457</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT11" t="n">
         <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.005948749601782781</v>
+        <v>0.07309760080959238</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,64 +6348,64 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.01698076285864772</v>
+        <v>-0.002580360631365666</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.002006922168451553</v>
+        <v>-0.0438985823743694</v>
       </c>
       <c r="CA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="n">
         <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.01025442956341493</v>
+        <v>-0.1121727072795386</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.01993208158208705</v>
+        <v>-0.03594434562456197</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.02939300629758319</v>
+        <v>0.1025850982739211</v>
       </c>
       <c r="CJ11" t="n">
         <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL11" t="n">
         <v>-0</v>
       </c>
       <c r="CM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.003845997257540931</v>
+        <v>-0.1211628963030538</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.02127993538163792</v>
+        <v>0.05023932198153961</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.02647547888069253</v>
+        <v>0.026631951844374</v>
       </c>
       <c r="CS11" t="n">
         <v>0</v>
@@ -6414,31 +6414,31 @@
         <v>0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
         <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.02437046337995839</v>
+        <v>-0.09657014219611858</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>-0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0180450700039775</v>
+        <v>-0.03537464411392137</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.01870732885789028</v>
+        <v>0.1033584473112995</v>
       </c>
       <c r="DB11" t="n">
         <v>-0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
@@ -6447,49 +6447,49 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.01870666985183548</v>
+        <v>-0.1012214773021515</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>-0.006857992685443973</v>
+        <v>-0.1122074750950724</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.02706548692725664</v>
+        <v>0.09969654170511694</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.008454850164377744</v>
+        <v>-0.04902566287996792</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.02773998555624205</v>
+        <v>-0.02752120671871564</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.007252209393700915</v>
+        <v>0.01876126648980337</v>
       </c>
       <c r="DT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU11" t="n">
         <v>-0</v>
@@ -6498,25 +6498,25 @@
         <v>-0</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.009582949614666204</v>
+        <v>-0.02285991963122067</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.03503233813249097</v>
+        <v>-0.001644375230361122</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.01228085284398256</v>
+        <v>0.04694730080313778</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
         <v>0</v>
@@ -6528,34 +6528,34 @@
         <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.0186785895551904</v>
+        <v>-0.07059092319734754</v>
       </c>
       <c r="EH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.00859659915679456</v>
+        <v>-0.08955373401666285</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.005435677615162528</v>
+        <v>0.06231468323625799</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.007011453806346751</v>
+        <v>-0.0381138444992662</v>
       </c>
       <c r="EQ11" t="n">
         <v>-0</v>
@@ -6564,25 +6564,25 @@
         <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.007097984400369265</v>
+        <v>-0.09878583432952288</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.01786097275298205</v>
+        <v>0.1427475481617945</v>
       </c>
       <c r="EU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX11" t="n">
         <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.01741030312155034</v>
+        <v>-0.1145639936650969</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
@@ -6591,16 +6591,16 @@
         <v>0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.02467364925207881</v>
+        <v>-0.06515021947548573</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.02488249548060708</v>
+        <v>0.08930949358854197</v>
       </c>
       <c r="FD11" t="n">
         <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
         <v>-0</v>
@@ -6609,7 +6609,7 @@
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.004333476382012705</v>
+        <v>-0.1483005649896154</v>
       </c>
       <c r="FI11" t="n">
         <v>0</v>
@@ -6618,16 +6618,16 @@
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.05032848945922486</v>
+        <v>0.04616404444481968</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.03899328528266449</v>
+        <v>0.08956900801800592</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
@@ -6636,7 +6636,7 @@
         <v>0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.01609290963891969</v>
+        <v>0.05525821038246407</v>
       </c>
       <c r="FR11" t="n">
         <v>0</v>
@@ -6645,28 +6645,28 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.03171223567700426</v>
+        <v>0.09201763391607391</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.0429811729857278</v>
+        <v>0.03288174033806424</v>
       </c>
       <c r="FV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.04099944574310734</v>
+        <v>-0.05845874025277331</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
@@ -6675,13 +6675,13 @@
         <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.03382681837060292</v>
+        <v>0.1120096275456793</v>
       </c>
       <c r="GE11" t="n">
         <v>0</v>
       </c>
       <c r="GF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG11" t="n">
         <v>0</v>
@@ -6692,22 +6692,22 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.378124878595656</v>
+        <v>0.3826453365309224</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2733130796506011</v>
+        <v>-0.2778945007858266</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1226292057509738</v>
+        <v>-0.01070918406245947</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
@@ -6716,22 +6716,22 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2517226750030906</v>
+        <v>0.3751605899712055</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2831430067298677</v>
+        <v>-0.3624415481523061</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1121719640071306</v>
+        <v>-0.04260293849229202</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12" t="n">
         <v>-0</v>
@@ -6743,28 +6743,28 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.04046266717227329</v>
+        <v>0.02620100398874755</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.005800475441373032</v>
+        <v>-0.01863220847907884</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.02653572870747191</v>
+        <v>-0.02644809714938246</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -6773,43 +6773,43 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1662723636510726</v>
+        <v>-0.06226981190161561</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.108385029311742</v>
+        <v>-0.07404981580841895</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.03633026151399812</v>
+        <v>-0.04112105738900532</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.04546769219821116</v>
+        <v>0.1232039446747198</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.04134900517087813</v>
+        <v>-0.1107892980852506</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.09785175581678929</v>
+        <v>0.06692871485567553</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6824,19 +6824,19 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.3579490354898502</v>
+        <v>0.253227162143155</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.05391795559968948</v>
+        <v>-0.1868893499028738</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.002834621325823204</v>
+        <v>-0.1125992081893619</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
@@ -6848,22 +6848,22 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.01324995822945175</v>
+        <v>0.03588372036028988</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.09183558406425521</v>
+        <v>-0.02450658086172183</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1924134717110207</v>
+        <v>-0.002280396198066058</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,49 +6881,49 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.09967437288945973</v>
+        <v>-0.0672969725998547</v>
       </c>
       <c r="BN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.07609120666476359</v>
+        <v>0.0255957821629026</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.01780672321791369</v>
+        <v>0.04269006303818459</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU12" t="n">
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.08457508727216646</v>
+        <v>0.09301776675086967</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.007260268640432484</v>
+        <v>-0.01572864322848867</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.0277960286906393</v>
+        <v>-0.0005859005728554952</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
         <v>0</v>
@@ -6935,46 +6935,46 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1071730981805553</v>
+        <v>-0.1690123274945686</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.01387602752290927</v>
+        <v>0.1644141117125077</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.01184999181078431</v>
+        <v>-0.006611661079515989</v>
       </c>
       <c r="CI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.03572634179581544</v>
+        <v>-0.138124264854721</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.1593014175027933</v>
+        <v>0.2679691822344215</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.07899213753122027</v>
+        <v>0.01634423902374965</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6983,55 +6983,55 @@
         <v>-0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.08054157957479378</v>
+        <v>-0.165005470597274</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.04477101773764684</v>
+        <v>0.1574804437650215</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.006752025696656393</v>
+        <v>0.007442950068104573</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.05207534824716519</v>
+        <v>-0.09622142912195161</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.03202634068116704</v>
+        <v>0.0286912383565583</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.1210441840739453</v>
+        <v>-0.07078964940485898</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.1110999843003107</v>
+        <v>-0.09725051531830727</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.05854427135451871</v>
+        <v>0.06616560199810284</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.04936209151338139</v>
+        <v>0.004098955082275741</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
@@ -7070,25 +7070,25 @@
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.0004438977364589661</v>
+        <v>-0.004928524025098277</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.09235112902357161</v>
+        <v>-0.1122378449251885</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.1250737533650929</v>
+        <v>0.06879976411259835</v>
       </c>
       <c r="EB12" t="n">
         <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
@@ -7097,97 +7097,97 @@
         <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.02029625710266626</v>
+        <v>-0.1238941325386419</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.04045015299880296</v>
+        <v>0.133291188913954</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.0659367383708454</v>
+        <v>0.05165820380386524</v>
       </c>
       <c r="EK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.07587632164871774</v>
+        <v>-0.1455897195689743</v>
       </c>
       <c r="EQ12" t="n">
         <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.08153850012892963</v>
+        <v>0.105860243608818</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.05989521966743993</v>
+        <v>0.02311889877939584</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX12" t="n">
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.07674417245805827</v>
+        <v>-0.1780676452223743</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.05169358807062307</v>
+        <v>0.1860300594469948</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.009224070370734857</v>
+        <v>-0.01379096415509836</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.007533296319443714</v>
+        <v>-0.09560378591701403</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.06288530570205553</v>
+        <v>0.05438262905997432</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.0715667846459308</v>
+        <v>-0.02996376956195924</v>
       </c>
       <c r="FL12" t="n">
         <v>0</v>
@@ -7199,61 +7199,61 @@
         <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.03154411395321903</v>
+        <v>0.1383024768807042</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.01253363637163566</v>
+        <v>0.164783379537745</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.2158597836045986</v>
+        <v>0.1054575266894001</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
         <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.02687395581794321</v>
+        <v>-0.1115997772665582</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.01769328572875879</v>
+        <v>0.1057025824686576</v>
       </c>
       <c r="GC12" t="n">
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,7 +7261,7 @@
         <v>-0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.08157742664299317</v>
+        <v>0.2700796684519908</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,10 +7270,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.01032329612064652</v>
+        <v>0.01923718771250968</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1498532613759205</v>
+        <v>-0.3105409640176491</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7285,10 +7285,10 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.06251573698731598</v>
+        <v>0.3381671753554873</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,10 +7297,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.01384694986003267</v>
+        <v>-0.02284796710992876</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.144361825892711</v>
+        <v>-0.2737624872061408</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -7309,13 +7309,13 @@
         <v>-0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0005672347857943953</v>
+        <v>-0.003099304380904946</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -7324,16 +7324,16 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.01234502410105535</v>
+        <v>-0.09376224048911824</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.008901326409910683</v>
+        <v>-0.039976280191747</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -7342,19 +7342,19 @@
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0258013699816003</v>
+        <v>-0.1436111654491689</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.04382667736609726</v>
+        <v>-0.1961984441724821</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.01483156882260743</v>
+        <v>-0.169887379193175</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -7363,28 +7363,28 @@
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.003177920889564754</v>
+        <v>0.06544760261020267</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.008611899194274172</v>
+        <v>-0.0110471318711048</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.01241228263962934</v>
+        <v>-0.07627244029586866</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7396,19 +7396,19 @@
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.07276525709726678</v>
+        <v>0.3725945259091691</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.009260944316436714</v>
+        <v>-0.07450365885853534</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.05689638643317031</v>
+        <v>-0.06142746046063789</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -7420,37 +7420,37 @@
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.03557798720538842</v>
+        <v>-0.02840300029927888</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.03265159507646977</v>
+        <v>-0.1426264051596305</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.07319383694515448</v>
+        <v>-0.2898846622371014</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
         <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
         <v>-0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.04178363367997673</v>
+        <v>0.01143974182277361</v>
       </c>
       <c r="BN13" t="n">
         <v>-0</v>
@@ -7459,13 +7459,13 @@
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.04240073955727137</v>
+        <v>0.0652114785807509</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.001909179500058609</v>
+        <v>0.07175806147100729</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.01154006639744645</v>
+        <v>0.07481436777600202</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0001302238854406938</v>
+        <v>-0.0547077986246657</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.02185468428920267</v>
+        <v>-0.08919242668372883</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB13" t="n">
         <v>0</v>
@@ -7504,19 +7504,19 @@
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.01482288591317391</v>
+        <v>-0.07880271411152931</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-2.093808436756747e-05</v>
+        <v>-0.00306637017848401</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.03863754876790438</v>
+        <v>0.1422147099985105</v>
       </c>
       <c r="CJ13" t="n">
         <v>-0</v>
@@ -7531,7 +7531,7 @@
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.01461937157666344</v>
+        <v>-0.1497768440939354</v>
       </c>
       <c r="CO13" t="n">
         <v>0</v>
@@ -7540,37 +7540,37 @@
         <v>0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.01755310836278854</v>
+        <v>0.2681634913098697</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.01417738570416528</v>
+        <v>0.2472122398325823</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
         <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.005042212508825501</v>
+        <v>-0.06911158458785294</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.002281284280522716</v>
+        <v>0.0005835745513454466</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0295667767650077</v>
+        <v>0.1271908993804938</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
@@ -7585,100 +7585,100 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.005304406592055547</v>
+        <v>-0.04458287094136059</v>
       </c>
       <c r="DG13" t="n">
         <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.02228783610975511</v>
+        <v>-0.08363310132637414</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.04141262964579338</v>
+        <v>-0.01199142619099251</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM13" t="n">
         <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.01585691351219012</v>
+        <v>0.006008865400552013</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.03527241155533142</v>
+        <v>0.1075126072953314</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.04035122705135693</v>
+        <v>0.1639503784554584</v>
       </c>
       <c r="DT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.01557713298468164</v>
+        <v>-0.008885647202977158</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.001085147223323146</v>
+        <v>0.08590161520269654</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.03775630044931529</v>
+        <v>0.1074381932371002</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
         <v>-0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.01583596252709332</v>
+        <v>-0.1185542057663316</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>-0.005069143019532638</v>
+        <v>-0.02659474936150267</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.002451691143446478</v>
+        <v>0.02202408574958985</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
@@ -7687,28 +7687,28 @@
         <v>0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.0168899550611639</v>
+        <v>0.02061329304444641</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.02718570222890129</v>
+        <v>-0.03023468415764714</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.04429755848748013</v>
+        <v>0.1223244549725956</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
@@ -7720,19 +7720,19 @@
         <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.009173241749480799</v>
+        <v>-0.0908769797435663</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
         <v>0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.005441235268620958</v>
+        <v>-0.0297935991558082</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.03101592977259685</v>
+        <v>0.1252181858746634</v>
       </c>
       <c r="FD13" t="n">
         <v>-0</v>
@@ -7747,34 +7747,34 @@
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.02610793744701512</v>
+        <v>-0.1433171877304988</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.008465150408975899</v>
+        <v>0.01370367769274292</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.03719787000569459</v>
+        <v>0.02285813133770866</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO13" t="n">
         <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.001387564004349046</v>
+        <v>0.05673615549631378</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
@@ -7783,10 +7783,10 @@
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.03784675797383504</v>
+        <v>0.1812288617092459</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0.01013058605209463</v>
+        <v>-0.02319794921277017</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
@@ -7795,16 +7795,16 @@
         <v>-0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.02247492688832588</v>
+        <v>-0.049776310524298</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
         <v>-0</v>
@@ -7813,16 +7813,16 @@
         <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.01808843347046455</v>
+        <v>0.09992560612486542</v>
       </c>
       <c r="GE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -7830,19 +7830,19 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.7393328673483063</v>
+        <v>0.2453871999116984</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3582462790928939</v>
+        <v>-0.1290150589240346</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1463697397491049</v>
+        <v>-0.02660055050100309</v>
       </c>
       <c r="F14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>-0</v>
@@ -7851,25 +7851,25 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4141180663614047</v>
+        <v>0.2050999657581545</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3474592389823863</v>
+        <v>-0.1881012803145259</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1661205865534058</v>
+        <v>-0.03578623269669583</v>
       </c>
       <c r="O14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>-0</v>
@@ -7881,82 +7881,82 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1436890162579034</v>
+        <v>0.02170105670527767</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.03001865469936027</v>
+        <v>-0.006330213566543333</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01199547336725208</v>
+        <v>0.005524302318010179</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.1338365753605902</v>
+        <v>-0.05218940482606136</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.01999125289675142</v>
+        <v>-0.1539622505164089</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.02062150053987606</v>
+        <v>-0.07284966762926984</v>
       </c>
       <c r="AG14" t="n">
         <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.002381461056556593</v>
+        <v>0.1040703385466663</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.08943551894786346</v>
+        <v>-0.05929066310262383</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.1098155461450637</v>
+        <v>0.06702626745922868</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
@@ -7965,25 +7965,25 @@
         <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.5843541440462621</v>
+        <v>0.2015628434654367</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0.002674616181336853</v>
+        <v>-0.001782932923673709</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0772565189886215</v>
+        <v>-0.02950494118970936</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
@@ -7992,49 +7992,49 @@
         <v>-0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.07284007187368589</v>
+        <v>0.02164727269684379</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.2173372476388069</v>
+        <v>-0.05632644753050797</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.294026035679511</v>
+        <v>-0.04415055367392558</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI14" t="n">
         <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL14" t="n">
         <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.1815794044764897</v>
+        <v>0.02804097161923082</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.04319435735206634</v>
+        <v>0.0199534039685618</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.2435814389440039</v>
+        <v>0.1346398124891206</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
@@ -8046,19 +8046,19 @@
         <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.2570084533689166</v>
+        <v>0.1710410744960336</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX14" t="n">
-        <v>-0.005736268555961897</v>
+        <v>-0.01747475270507382</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.01704147005912708</v>
+        <v>0.01983562666009903</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
@@ -8067,25 +8067,25 @@
         <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.1566415554087251</v>
+        <v>-0.08314018632496616</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0390347259948625</v>
+        <v>0.07278735269212683</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.016513140541541</v>
+        <v>0.02388292759088853</v>
       </c>
       <c r="CI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ14" t="n">
         <v>-0</v>
@@ -8094,52 +8094,52 @@
         <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM14" t="n">
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.003482718419654838</v>
+        <v>-0.1407104797130907</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.1450546789679125</v>
+        <v>0.1542215743746293</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.1476469088150788</v>
+        <v>-0.02731648568510568</v>
       </c>
       <c r="CR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS14" t="n">
         <v>-0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.1355035397743315</v>
+        <v>-0.07263847303963643</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.06804731129753708</v>
+        <v>0.07335807496675945</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.01144375353941781</v>
+        <v>0.02706697258459132</v>
       </c>
       <c r="DA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB14" t="n">
         <v>0</v>
@@ -8148,22 +8148,22 @@
         <v>-0</v>
       </c>
       <c r="DD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.009361681127414784</v>
+        <v>0.00311362801148317</v>
       </c>
       <c r="DG14" t="n">
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.04218073402523247</v>
+        <v>-0.00699481168981395</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.0296627822218841</v>
+        <v>-0.04059307333836975</v>
       </c>
       <c r="DJ14" t="n">
         <v>-0</v>
@@ -8172,79 +8172,79 @@
         <v>0</v>
       </c>
       <c r="DL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM14" t="n">
         <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.05302446108120482</v>
+        <v>-0.1140728489553391</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.06713263234349556</v>
+        <v>-0.04218010477338177</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.04465375856345443</v>
+        <v>0.06686031202883276</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.06983558809059812</v>
+        <v>0.05615778603448977</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.001289874998924258</v>
+        <v>0.04061587812235391</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.03714000333891646</v>
+        <v>-0.06631041939587964</v>
       </c>
       <c r="EB14" t="n">
         <v>0</v>
       </c>
       <c r="EC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.1164007995873581</v>
+        <v>-0.008548323890384069</v>
       </c>
       <c r="EH14" t="n">
         <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.07750818709390188</v>
+        <v>0.0583362173947649</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.09039748389395195</v>
+        <v>0.08022273841132614</v>
       </c>
       <c r="EK14" t="n">
         <v>0</v>
@@ -8253,7 +8253,7 @@
         <v>-0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
         <v>-0</v>
@@ -8262,43 +8262,43 @@
         <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.1308723212628531</v>
+        <v>-0.04797160942249388</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.05984774186035339</v>
+        <v>0.05945479390193947</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.02849808249566096</v>
+        <v>-0.02791798289544463</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW14" t="n">
         <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.1421140393088027</v>
+        <v>-0.0862095126163913</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.05199504959249526</v>
+        <v>0.08394796035415719</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.01865452714726427</v>
+        <v>0.006907522678985262</v>
       </c>
       <c r="FC14" t="n">
         <v>-0</v>
@@ -8310,58 +8310,58 @@
         <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.01640386394279725</v>
+        <v>0.00464980122626365</v>
       </c>
       <c r="FI14" t="n">
         <v>-0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.09093644858569626</v>
+        <v>0.006731527529600137</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.04752091342332028</v>
+        <v>-0.1069648169920855</v>
       </c>
       <c r="FL14" t="n">
         <v>-0</v>
       </c>
       <c r="FM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.01077299943182079</v>
+        <v>-0.009989448174140783</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>-0.04052424620081697</v>
+        <v>0.03662726227764102</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.01819285643652068</v>
+        <v>-0.03677661853294067</v>
       </c>
       <c r="FU14" t="n">
         <v>-0</v>
       </c>
       <c r="FV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
         <v>0</v>
@@ -8370,25 +8370,25 @@
         <v>-0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.02606721046393131</v>
+        <v>-0.06995020041588115</v>
       </c>
       <c r="GA14" t="n">
         <v>-0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.071008982809843</v>
+        <v>0.04622439899194169</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
         <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG14" t="n">
         <v>-0</v>
@@ -8399,25 +8399,25 @@
         <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.546209796427664</v>
+        <v>-0.6001421337328929</v>
       </c>
       <c r="C15" t="n">
         <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1858654900802911</v>
+        <v>0.2120284142035135</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1327764729324755</v>
+        <v>0.1785668474907977</v>
       </c>
       <c r="F15" t="n">
         <v>-0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>-0</v>
@@ -8426,46 +8426,46 @@
         <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.37213556805839</v>
+        <v>-0.4776764945114811</v>
       </c>
       <c r="L15" t="n">
         <v>-0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2160029379438447</v>
+        <v>0.3474364010527519</v>
       </c>
       <c r="N15" t="n">
-        <v>0.05225728838798648</v>
+        <v>0.2580867009995219</v>
       </c>
       <c r="O15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>-0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1268024287414563</v>
+        <v>-0.0540120632404785</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0302583837307627</v>
+        <v>0.07266684460604349</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.0217818627105091</v>
+        <v>-0.02823123102153126</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -8477,55 +8477,55 @@
         <v>-0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.2003168435292739</v>
+        <v>-0.04541333554603733</v>
       </c>
       <c r="AD15" t="n">
         <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.0632766536945247</v>
+        <v>0.1823420476214686</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.03453334968552078</v>
+        <v>-0.0109961269689787</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.05128912688076755</v>
+        <v>-0.2380182179918772</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.03745176180852271</v>
+        <v>0.06754378396311832</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.03335720884946377</v>
+        <v>-0.2017083489570274</v>
       </c>
       <c r="AP15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
         <v>-0</v>
@@ -8534,22 +8534,22 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.3332650885688035</v>
+        <v>-0.5072228708336664</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0.07367668034459918</v>
+        <v>0.1799382249023323</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.02629328644358156</v>
+        <v>0.0775667036448936</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA15" t="n">
         <v>-0</v>
@@ -8561,25 +8561,25 @@
         <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>-0.1035075498902999</v>
+        <v>0.05145803781851825</v>
       </c>
       <c r="BE15" t="n">
         <v>-0</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.1154469530572646</v>
+        <v>0.005863703393433815</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.3459586580195336</v>
+        <v>0.2146552433692025</v>
       </c>
       <c r="BH15" t="n">
         <v>-0</v>
       </c>
       <c r="BI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK15" t="n">
         <v>-0</v>
@@ -8588,43 +8588,43 @@
         <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.009215395773566226</v>
+        <v>0.0705383956882252</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
       </c>
       <c r="BO15" t="n">
-        <v>-0.0534790711153284</v>
+        <v>0.007345180859889538</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.0951806975556547</v>
+        <v>0.05694084171810197</v>
       </c>
       <c r="BQ15" t="n">
         <v>0</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
         <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>-0.2083581837171749</v>
+        <v>-0.3774369430912973</v>
       </c>
       <c r="BW15" t="n">
         <v>-0</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.05783055174457597</v>
+        <v>0.1768469919189883</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.03962131997593572</v>
+        <v>0.01953218454187473</v>
       </c>
       <c r="BZ15" t="n">
         <v>-0</v>
@@ -8633,7 +8633,7 @@
         <v>0</v>
       </c>
       <c r="CB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC15" t="n">
         <v>-0</v>
@@ -8642,46 +8642,46 @@
         <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.117010121387529</v>
+        <v>0.2684610244588033</v>
       </c>
       <c r="CF15" t="n">
         <v>0</v>
       </c>
       <c r="CG15" t="n">
-        <v>-0.0326644026118451</v>
+        <v>-0.05884479474774815</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.05868676450726951</v>
+        <v>-0.03665624050956996</v>
       </c>
       <c r="CI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM15" t="n">
         <v>-0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.04281947951734864</v>
+        <v>0.309529088172168</v>
       </c>
       <c r="CO15" t="n">
         <v>0</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.00155283021658989</v>
+        <v>-0.09468707128779678</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.0007164144174470265</v>
+        <v>-0.2878969431281863</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS15" t="n">
         <v>0</v>
@@ -8696,76 +8696,76 @@
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.119284090763695</v>
+        <v>0.2673789722687499</v>
       </c>
       <c r="CX15" t="n">
         <v>-0</v>
       </c>
       <c r="CY15" t="n">
-        <v>-0.048186692224403</v>
+        <v>-0.08618379915533519</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.03864045779138892</v>
+        <v>-0.05141558742420917</v>
       </c>
       <c r="DA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.1210130971474241</v>
+        <v>0.03800272094503447</v>
       </c>
       <c r="DG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0.03753142871149698</v>
+        <v>-0.01835660432728849</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.0009523626789875843</v>
+        <v>-0.004481368362581057</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL15" t="n">
         <v>-0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.1222907463060082</v>
+        <v>0.1749102545133295</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0.07007462677468208</v>
+        <v>-0.01603840934510659</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.1480871025717462</v>
+        <v>-0.006998783358514065</v>
       </c>
       <c r="DS15" t="n">
         <v>-0</v>
       </c>
       <c r="DT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
@@ -8774,22 +8774,22 @@
         <v>-0</v>
       </c>
       <c r="DW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.05383479355006177</v>
+        <v>0.04133313141183175</v>
       </c>
       <c r="DY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.1500510067302466</v>
+        <v>0.003792681054660392</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.08061568507191445</v>
+        <v>-0.07256881477014801</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC15" t="n">
         <v>0</v>
@@ -8804,25 +8804,25 @@
         <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.06462548997400741</v>
+        <v>0.2661192750231626</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>-0.00896180514946978</v>
+        <v>-0.04045194357287978</v>
       </c>
       <c r="EJ15" t="n">
-        <v>-0.0659901196659534</v>
+        <v>-0.02080597442115954</v>
       </c>
       <c r="EK15" t="n">
         <v>0</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN15" t="n">
         <v>-0</v>
@@ -8831,73 +8831,73 @@
         <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.06494090652742199</v>
+        <v>0.2144684799387203</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.06132792995975652</v>
+        <v>-0.09180942307699312</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.08258227407552629</v>
+        <v>-0.1458153593262748</v>
       </c>
       <c r="ET15" t="n">
         <v>0</v>
       </c>
       <c r="EU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX15" t="n">
         <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.136917296192299</v>
+        <v>0.3236584027092264</v>
       </c>
       <c r="EZ15" t="n">
         <v>0</v>
       </c>
       <c r="FA15" t="n">
-        <v>-0.06255594444344474</v>
+        <v>-0.06464517672620952</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.03296499847453138</v>
+        <v>-0.04566761606237318</v>
       </c>
       <c r="FC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG15" t="n">
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.03485771861461451</v>
+        <v>0.170986763056427</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>-0.05094803032547533</v>
+        <v>-0.08068240802290685</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.0357131750258787</v>
+        <v>-0.002010159646039881</v>
       </c>
       <c r="FL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM15" t="n">
         <v>-0</v>
@@ -8906,87 +8906,87 @@
         <v>-0</v>
       </c>
       <c r="FO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.01929992768514632</v>
+        <v>0.02629223245351704</v>
       </c>
       <c r="FR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.1452532068155744</v>
+        <v>-0.1840016901951821</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.03566726626817218</v>
+        <v>-0.033243502430522</v>
       </c>
       <c r="FU15" t="n">
         <v>0</v>
       </c>
       <c r="FV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.06538771596408724</v>
+        <v>0.1336709848814615</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.1033997663542421</v>
+        <v>0.02488063623448462</v>
       </c>
       <c r="GC15" t="n">
         <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE15" t="n">
         <v>0</v>
       </c>
       <c r="GF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.342970196518474</v>
+        <v>0.2031663683772587</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1097515327279935</v>
+        <v>-0.1407117156347355</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.07141131794219462</v>
+        <v>0.1427643468092199</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -8995,25 +8995,25 @@
         <v>-0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2738566767456348</v>
+        <v>0.2021514205452867</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1278609334685742</v>
+        <v>-0.165349930261914</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1402247354580816</v>
+        <v>0.06696808446069892</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -9025,19 +9025,19 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0898069982008298</v>
+        <v>0.03452980051202631</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.02219012329727756</v>
+        <v>-0.03994095573007739</v>
       </c>
       <c r="W16" t="n">
-        <v>0.03283356269470165</v>
+        <v>-0.04669255266767385</v>
       </c>
       <c r="X16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
         <v>-0</v>
@@ -9049,79 +9049,79 @@
         <v>-0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.06426784352370626</v>
+        <v>0.04553124553373938</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.04699573585661168</v>
+        <v>0.1024646800297219</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.02461271060332367</v>
+        <v>0.04310566225303637</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0.02307886884534528</v>
+        <v>0.05406391132964766</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0.03288830313013368</v>
+        <v>-0.05852119155206835</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.08425828309962584</v>
+        <v>0.0004626230667029018</v>
       </c>
       <c r="AP16" t="n">
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.1595743929262506</v>
+        <v>0.1993320463010466</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0.02322273317365001</v>
+        <v>-0.2268786571062467</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.1652389883018708</v>
+        <v>-0.01970227586730812</v>
       </c>
       <c r="AY16" t="n">
         <v>-0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>-0</v>
@@ -9130,16 +9130,16 @@
         <v>-0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.09872972827781143</v>
+        <v>-0.01238684023363018</v>
       </c>
       <c r="BF16" t="n">
-        <v>-0.04669224878704851</v>
+        <v>0.1340527273350162</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.08757230315296104</v>
+        <v>0.08115311813682992</v>
       </c>
       <c r="BH16" t="n">
         <v>0</v>
@@ -9154,49 +9154,49 @@
         <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.03983958074702239</v>
+        <v>-0.06030135854029023</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.05920005311724343</v>
+        <v>-0.08066455695969676</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.129933395322922</v>
+        <v>-0.1292020979343453</v>
       </c>
       <c r="BQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.05314719140800196</v>
+        <v>0.09721625055393802</v>
       </c>
       <c r="BX16" t="n">
-        <v>-0.01467073408744076</v>
+        <v>-0.0803368288880927</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.09636595815116242</v>
+        <v>-0.02546479956150703</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA16" t="n">
         <v>0</v>
@@ -9205,28 +9205,28 @@
         <v>-0</v>
       </c>
       <c r="CC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE16" t="n">
         <v>0</v>
       </c>
       <c r="CF16" t="n">
-        <v>-0.07198410961931657</v>
+        <v>-0.07861226057690586</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.02509372377254469</v>
+        <v>0.07268067817461352</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.002765312141491885</v>
+        <v>-0.03105972465713358</v>
       </c>
       <c r="CI16" t="n">
         <v>0</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
@@ -9235,19 +9235,19 @@
         <v>-0</v>
       </c>
       <c r="CM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO16" t="n">
-        <v>0.0157259551637416</v>
+        <v>-0.0152213403069345</v>
       </c>
       <c r="CP16" t="n">
-        <v>-0.007232599217462946</v>
+        <v>0.17202042509536</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.134030388334011</v>
+        <v>0.01983684806665717</v>
       </c>
       <c r="CR16" t="n">
         <v>0</v>
@@ -9256,34 +9256,34 @@
         <v>0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU16" t="n">
         <v>-0</v>
       </c>
       <c r="CV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0.05447512606266257</v>
+        <v>-0.05784014068397651</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.02501838199046121</v>
+        <v>0.07015821153237836</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.02713359366719531</v>
+        <v>-0.04650525817935287</v>
       </c>
       <c r="DA16" t="n">
         <v>-0</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD16" t="n">
         <v>0</v>
@@ -9292,16 +9292,16 @@
         <v>-0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG16" t="n">
-        <v>-0.03707849523066748</v>
+        <v>-0.01125498461567062</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.04550360450758483</v>
+        <v>0.02739623101615173</v>
       </c>
       <c r="DI16" t="n">
-        <v>-0.00680358613817661</v>
+        <v>-0.02331957611138215</v>
       </c>
       <c r="DJ16" t="n">
         <v>0</v>
@@ -9313,31 +9313,31 @@
         <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
         <v>-0</v>
       </c>
       <c r="DP16" t="n">
-        <v>-0.003156122121830755</v>
+        <v>-0.02302751005764581</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.02956404662718841</v>
+        <v>0.06371845925258245</v>
       </c>
       <c r="DR16" t="n">
-        <v>-0.1504434517564663</v>
+        <v>-0.06197546923819081</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV16" t="n">
         <v>0</v>
@@ -9346,16 +9346,16 @@
         <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.06134807659331291</v>
+        <v>0.02436552677783661</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.003502486305162758</v>
+        <v>0.02514121832756418</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.06389529179402857</v>
+        <v>0.04441827750162265</v>
       </c>
       <c r="EB16" t="n">
         <v>0</v>
@@ -9370,46 +9370,46 @@
         <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH16" t="n">
-        <v>-0.1143604660715261</v>
+        <v>-0.03995863905222927</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.05244576720599337</v>
+        <v>0.04788642181336052</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.06638098822878905</v>
+        <v>0.01786017429252081</v>
       </c>
       <c r="EK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN16" t="n">
         <v>-0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
         <v>0</v>
       </c>
       <c r="EQ16" t="n">
-        <v>-0.007602853461317472</v>
+        <v>-0.04669092531631137</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.03277591048267625</v>
+        <v>0.07629484031189114</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.02644310966726408</v>
+        <v>0.01524621880531175</v>
       </c>
       <c r="ET16" t="n">
         <v>0</v>
@@ -9418,79 +9418,79 @@
         <v>0</v>
       </c>
       <c r="EV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ16" t="n">
-        <v>-0.06821644659536467</v>
+        <v>-0.06468576665128063</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.04100492745836462</v>
+        <v>0.1084687177008568</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.02452896192668477</v>
+        <v>-0.03010400741768713</v>
       </c>
       <c r="FC16" t="n">
         <v>0</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG16" t="n">
         <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0.005158136240674969</v>
+        <v>-0.01754975497858886</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.0011531778052613</v>
+        <v>0.06082317921820336</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.07860345749122406</v>
+        <v>-0.03365918797016241</v>
       </c>
       <c r="FL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO16" t="n">
         <v>-0</v>
       </c>
       <c r="FP16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR16" t="n">
-        <v>-0.004244804252954616</v>
+        <v>-0.0003744790256449767</v>
       </c>
       <c r="FS16" t="n">
-        <v>-0.007227238551969782</v>
+        <v>-0.00771373471782752</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.0967967429214432</v>
+        <v>0.2238947733548228</v>
       </c>
       <c r="FU16" t="n">
         <v>0</v>
@@ -9499,22 +9499,22 @@
         <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.05079393359683145</v>
+        <v>-0.02559187322135254</v>
       </c>
       <c r="GB16" t="n">
-        <v>-0.04844318096004517</v>
+        <v>0.1451283228112003</v>
       </c>
       <c r="GC16" t="n">
         <v>-0</v>
@@ -9537,22 +9537,22 @@
         <v>-0</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.2522417388984197</v>
+        <v>-0.270882898152466</v>
       </c>
       <c r="C17" t="n">
         <v>-0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3555819454258746</v>
+        <v>0.07461694997335368</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9376872490640334</v>
+        <v>0.3525372615466967</v>
       </c>
       <c r="G17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -9564,7 +9564,7 @@
         <v>-0</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2279330814242219</v>
+        <v>-0.2419904023244663</v>
       </c>
       <c r="L17" t="n">
         <v>-0</v>
@@ -9573,10 +9573,10 @@
         <v>-0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3489775222388402</v>
+        <v>0.1938172923776949</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7527365532307281</v>
+        <v>0.2880074576129809</v>
       </c>
       <c r="P17" t="n">
         <v>-0</v>
@@ -9591,22 +9591,22 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.03505482237846016</v>
+        <v>-0.06190689960976468</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V17" t="n">
         <v>-0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0178964885517884</v>
+        <v>0.08549280529238326</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1032566813602111</v>
+        <v>0.01749222389627856</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -9615,22 +9615,22 @@
         <v>-0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.07120656509002858</v>
+        <v>-0.01307991790369076</v>
       </c>
       <c r="AD17" t="n">
         <v>-0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.1191441618537049</v>
+        <v>0.1541168642701767</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.0709193104892494</v>
+        <v>0.06038467064809384</v>
       </c>
       <c r="AH17" t="n">
         <v>-0</v>
@@ -9639,28 +9639,28 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK17" t="n">
         <v>-0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.01210109388651744</v>
+        <v>-0.1317177483088792</v>
       </c>
       <c r="AM17" t="n">
         <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.08212798343526145</v>
+        <v>-0.04688278852133085</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.1339004182639238</v>
+        <v>0.09942443406658895</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -9669,49 +9669,49 @@
         <v>-0</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU17" t="n">
-        <v>-0.06864689510343366</v>
+        <v>-0.3036942599761991</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>-0.04417087284402579</v>
+        <v>0.1252405898491979</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.4277892449536332</v>
+        <v>0.1616522314045085</v>
       </c>
       <c r="AZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
         <v>-0</v>
       </c>
       <c r="BD17" t="n">
-        <v>-0.2053232061645263</v>
+        <v>0.01714890849535421</v>
       </c>
       <c r="BE17" t="n">
         <v>-0</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.04354118282295492</v>
+        <v>0.1506533424839442</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.2797344161551931</v>
+        <v>0.1020022327378811</v>
       </c>
       <c r="BI17" t="n">
         <v>-0</v>
@@ -9720,13 +9720,13 @@
         <v>0</v>
       </c>
       <c r="BK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL17" t="n">
         <v>-0</v>
       </c>
       <c r="BM17" t="n">
-        <v>-0.05731961359152688</v>
+        <v>-0.01398245762864202</v>
       </c>
       <c r="BN17" t="n">
         <v>0</v>
@@ -9735,13 +9735,13 @@
         <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>-0.03449166945187442</v>
+        <v>-0.08543052872108543</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.06793768519851884</v>
+        <v>-0.02230104661223105</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS17" t="n">
         <v>-0</v>
@@ -9753,49 +9753,49 @@
         <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.005841159922310395</v>
+        <v>-0.1586699409291602</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>-0.04587473894242786</v>
+        <v>0.06576513730360833</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.3034794440231323</v>
+        <v>0.1121120581584971</v>
       </c>
       <c r="CA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB17" t="n">
         <v>0</v>
       </c>
       <c r="CC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
         <v>0</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.06631759443131352</v>
+        <v>0.1011603792080142</v>
       </c>
       <c r="CF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.08057278404511396</v>
+        <v>-0.02867036237865437</v>
       </c>
       <c r="CI17" t="n">
-        <v>-0.1225298537445581</v>
+        <v>-0.08375231509063019</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK17" t="n">
         <v>-0</v>
@@ -9804,28 +9804,28 @@
         <v>-0</v>
       </c>
       <c r="CM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.05381396217216972</v>
+        <v>0.1511803222070015</v>
       </c>
       <c r="CO17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.2256315891771361</v>
+        <v>-0.1976820028391769</v>
       </c>
       <c r="CR17" t="n">
-        <v>0.08054893000587018</v>
+        <v>-0.06559527392541444</v>
       </c>
       <c r="CS17" t="n">
         <v>-0</v>
       </c>
       <c r="CT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU17" t="n">
         <v>0</v>
@@ -9834,19 +9834,19 @@
         <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>0.06840986987285604</v>
+        <v>0.08291283108821924</v>
       </c>
       <c r="CX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.04745818842894682</v>
+        <v>-0.03514191763504477</v>
       </c>
       <c r="DA17" t="n">
-        <v>-0.1177911192601196</v>
+        <v>-0.09720693603703276</v>
       </c>
       <c r="DB17" t="n">
         <v>-0</v>
@@ -9855,52 +9855,52 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE17" t="n">
         <v>-0</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.03908834128512888</v>
+        <v>0.03506801422031398</v>
       </c>
       <c r="DG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.02965071864288949</v>
+        <v>0.02172127500142701</v>
       </c>
       <c r="DJ17" t="n">
-        <v>-0.01350700871079513</v>
+        <v>-0.03995334123817956</v>
       </c>
       <c r="DK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL17" t="n">
         <v>-0</v>
       </c>
       <c r="DM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.02819024879412505</v>
+        <v>-0.006240510592977514</v>
       </c>
       <c r="DP17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ17" t="n">
         <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.006427089550697727</v>
+        <v>0.0470955959964233</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.01537158495180454</v>
+        <v>-0.01084738347153999</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
@@ -9915,46 +9915,46 @@
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.05509009402994478</v>
+        <v>-0.04168073698154528</v>
       </c>
       <c r="DY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ17" t="n">
         <v>-0</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.04832181087275859</v>
+        <v>0.03158566715415434</v>
       </c>
       <c r="EB17" t="n">
-        <v>-0.08093476203315494</v>
+        <v>0.003625771789836639</v>
       </c>
       <c r="EC17" t="n">
         <v>0</v>
       </c>
       <c r="ED17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.006044274492454821</v>
+        <v>0.04414202034847455</v>
       </c>
       <c r="EH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.0322212431533716</v>
+        <v>-0.01216177437687673</v>
       </c>
       <c r="EK17" t="n">
-        <v>-0.1070273534060086</v>
+        <v>-0.03487252105683603</v>
       </c>
       <c r="EL17" t="n">
         <v>0</v>
@@ -9969,7 +9969,7 @@
         <v>0</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.1663778337495811</v>
+        <v>0.07396722608138157</v>
       </c>
       <c r="EQ17" t="n">
         <v>0</v>
@@ -9978,10 +9978,10 @@
         <v>-0</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.04905244398374226</v>
+        <v>0.02799099122088572</v>
       </c>
       <c r="ET17" t="n">
-        <v>-0.06585900017908174</v>
+        <v>0.138958518993039</v>
       </c>
       <c r="EU17" t="n">
         <v>0</v>
@@ -9990,85 +9990,85 @@
         <v>-0</v>
       </c>
       <c r="EW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX17" t="n">
         <v>0</v>
       </c>
       <c r="EY17" t="n">
-        <v>0.07960054782456651</v>
+        <v>0.1133289702458214</v>
       </c>
       <c r="EZ17" t="n">
         <v>0</v>
       </c>
       <c r="FA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.04654217997812082</v>
+        <v>-0.02449817163226789</v>
       </c>
       <c r="FC17" t="n">
-        <v>-0.122348926020055</v>
+        <v>-0.08838630864922509</v>
       </c>
       <c r="FD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE17" t="n">
         <v>-0</v>
       </c>
       <c r="FF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG17" t="n">
         <v>-0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.05406957219163602</v>
+        <v>0.1029473352400945</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.02807232655490399</v>
+        <v>-0.06837497192220082</v>
       </c>
       <c r="FL17" t="n">
-        <v>-0.1488221249007662</v>
+        <v>-0.07856723265769079</v>
       </c>
       <c r="FM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN17" t="n">
         <v>-0</v>
       </c>
       <c r="FO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.009889436840908469</v>
+        <v>0.02970916870273703</v>
       </c>
       <c r="FR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT17" t="n">
-        <v>-0.02558915791179081</v>
+        <v>-0.01306313236407458</v>
       </c>
       <c r="FU17" t="n">
-        <v>-0.1846496305779978</v>
+        <v>-0.04832565089373789</v>
       </c>
       <c r="FV17" t="n">
         <v>0</v>
       </c>
       <c r="FW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX17" t="n">
         <v>-0</v>
@@ -10077,10 +10077,10 @@
         <v>-0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.06109323969379531</v>
+        <v>0.06826984852750882</v>
       </c>
       <c r="GA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB17" t="n">
         <v>0</v>
@@ -10089,10 +10089,10 @@
         <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0.007123439085700193</v>
+        <v>0.02221660308821012</v>
       </c>
       <c r="GE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF17" t="n">
         <v>0</v>
